--- a/public/fun/pack/xlsx/ledger/가계부_30_기업·소상공인_단풍든우체통.xlsx
+++ b/public/fun/pack/xlsx/ledger/가계부_30_기업·소상공인_단풍든우체통.xlsx
@@ -32,7 +32,7 @@
     <t>기업·소상공인 가계부</t>
   </si>
   <si>
-    <t>“붉은 우체통에 부치는 이번 달의 약속”</t>
+    <t>“연말정산 자료를 미리 모아 둡니다”</t>
   </si>
   <si>
     <t>단풍 든 우체통 테마</t>

--- a/public/fun/pack/xlsx/ledger/가계부_30_기업·소상공인_단풍든우체통.xlsx
+++ b/public/fun/pack/xlsx/ledger/가계부_30_기업·소상공인_단풍든우체통.xlsx
@@ -27,12 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="77">
   <si>
     <t>기업·소상공인 가계부</t>
-  </si>
-  <si>
-    <t>“연말정산 자료를 미리 모아 둡니다”</t>
   </si>
   <si>
     <t>단풍 든 우체통 테마</t>
@@ -1885,73 +1882,71 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="2:3" ht="6" customHeight="1"/>
     <row r="6" spans="2:3">
       <c r="B6" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="5"/>
     </row>
     <row r="7" spans="2:3" ht="22" customHeight="1">
       <c r="B7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>4</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="32" customHeight="1">
       <c r="B8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>6</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="32" customHeight="1">
       <c r="B9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>8</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="32" customHeight="1">
       <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>10</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="22" customHeight="1">
       <c r="B11" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>12</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="28" customHeight="1">
       <c r="B13" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" s="8"/>
     </row>
     <row r="15" spans="2:3">
       <c r="B15" s="9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -1988,7 +1983,7 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -1999,7 +1994,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -2010,25 +2005,25 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="F4" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="11" t="s">
         <v>49</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -2036,22 +2031,22 @@
         <v>46047</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>52</v>
       </c>
       <c r="E5" s="15">
         <v>18000000</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -2059,22 +2054,22 @@
         <v>46025</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E6" s="15">
         <v>6540000</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -2082,22 +2077,22 @@
         <v>46027</v>
       </c>
       <c r="B7" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E7" s="15">
         <v>2350000</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -2105,22 +2100,22 @@
         <v>46029</v>
       </c>
       <c r="B8" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E8" s="15">
         <v>4635000</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -2128,22 +2123,22 @@
         <v>46031</v>
       </c>
       <c r="B9" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E9" s="15">
         <v>792000</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -2151,22 +2146,22 @@
         <v>46033</v>
       </c>
       <c r="B10" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E10" s="15">
         <v>485000</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -2174,22 +2169,22 @@
         <v>46035</v>
       </c>
       <c r="B11" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E11" s="15">
         <v>371000</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -2197,22 +2192,22 @@
         <v>46037</v>
       </c>
       <c r="B12" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E12" s="15">
         <v>1092000</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -2220,22 +2215,22 @@
         <v>46039</v>
       </c>
       <c r="B13" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E13" s="15">
         <v>600000</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2243,22 +2238,22 @@
         <v>46041</v>
       </c>
       <c r="B14" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E14" s="15">
         <v>545000</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2266,22 +2261,22 @@
         <v>46043</v>
       </c>
       <c r="B15" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E15" s="15">
         <v>282000</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2289,22 +2284,22 @@
         <v>46078</v>
       </c>
       <c r="B16" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>52</v>
       </c>
       <c r="E16" s="15">
         <v>18000000</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -2312,22 +2307,22 @@
         <v>46056</v>
       </c>
       <c r="B17" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E17" s="15">
         <v>6360000</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2335,22 +2330,22 @@
         <v>46058</v>
       </c>
       <c r="B18" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E18" s="15">
         <v>2275000</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -2358,22 +2353,22 @@
         <v>46060</v>
       </c>
       <c r="B19" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E19" s="15">
         <v>4500000</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -2381,22 +2376,22 @@
         <v>46062</v>
       </c>
       <c r="B20" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D20" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E20" s="15">
         <v>981000</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -2404,22 +2399,22 @@
         <v>46064</v>
       </c>
       <c r="B21" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C21" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D21" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E21" s="15">
         <v>470000</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2427,22 +2422,22 @@
         <v>46066</v>
       </c>
       <c r="B22" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E22" s="15">
         <v>360000</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2450,22 +2445,22 @@
         <v>46068</v>
       </c>
       <c r="B23" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E23" s="15">
         <v>1056000</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -2473,22 +2468,22 @@
         <v>46070</v>
       </c>
       <c r="B24" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E24" s="15">
         <v>582000</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2496,22 +2491,22 @@
         <v>46072</v>
       </c>
       <c r="B25" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E25" s="15">
         <v>530000</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -2519,22 +2514,22 @@
         <v>46074</v>
       </c>
       <c r="B26" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E26" s="15">
         <v>273000</v>
       </c>
       <c r="F26" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2542,22 +2537,22 @@
         <v>46106</v>
       </c>
       <c r="B27" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D27" s="14" t="s">
-        <v>52</v>
       </c>
       <c r="E27" s="15">
         <v>18000000</v>
       </c>
       <c r="F27" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G27" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2565,22 +2560,22 @@
         <v>46084</v>
       </c>
       <c r="B28" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E28" s="15">
         <v>6180000</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2588,22 +2583,22 @@
         <v>46086</v>
       </c>
       <c r="B29" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C29" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D29" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E29" s="15">
         <v>2200000</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -2611,22 +2606,22 @@
         <v>46088</v>
       </c>
       <c r="B30" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C30" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E30" s="15">
         <v>4365000</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -2634,22 +2629,22 @@
         <v>46090</v>
       </c>
       <c r="B31" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D31" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C31" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E31" s="15">
         <v>954000</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -2657,22 +2652,22 @@
         <v>46092</v>
       </c>
       <c r="B32" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D32" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E32" s="15">
         <v>455000</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -2680,22 +2675,22 @@
         <v>46094</v>
       </c>
       <c r="B33" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D33" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D33" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E33" s="15">
         <v>350000</v>
       </c>
       <c r="F33" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -2703,22 +2698,22 @@
         <v>46096</v>
       </c>
       <c r="B34" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C34" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E34" s="15">
         <v>1308000</v>
       </c>
       <c r="F34" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -2726,22 +2721,22 @@
         <v>46098</v>
       </c>
       <c r="B35" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E35" s="15">
         <v>564000</v>
       </c>
       <c r="F35" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2749,22 +2744,22 @@
         <v>46100</v>
       </c>
       <c r="B36" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E36" s="15">
         <v>515000</v>
       </c>
       <c r="F36" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -2772,22 +2767,22 @@
         <v>46102</v>
       </c>
       <c r="B37" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D37" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E37" s="15">
         <v>264000</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -2795,22 +2790,22 @@
         <v>46137</v>
       </c>
       <c r="B38" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D38" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>52</v>
       </c>
       <c r="E38" s="15">
         <v>18000000</v>
       </c>
       <c r="F38" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -2818,22 +2813,22 @@
         <v>46115</v>
       </c>
       <c r="B39" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E39" s="15">
         <v>6000000</v>
       </c>
       <c r="F39" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G39" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2841,22 +2836,22 @@
         <v>46117</v>
       </c>
       <c r="B40" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E40" s="15">
         <v>2725000</v>
       </c>
       <c r="F40" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G40" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2864,22 +2859,22 @@
         <v>46119</v>
       </c>
       <c r="B41" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E41" s="15">
         <v>4230000</v>
       </c>
       <c r="F41" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -2887,22 +2882,22 @@
         <v>46121</v>
       </c>
       <c r="B42" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D42" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D42" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E42" s="15">
         <v>927000</v>
       </c>
       <c r="F42" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2910,22 +2905,22 @@
         <v>46123</v>
       </c>
       <c r="B43" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D43" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D43" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E43" s="15">
         <v>440000</v>
       </c>
       <c r="F43" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2933,22 +2928,22 @@
         <v>46125</v>
       </c>
       <c r="B44" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C44" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D44" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E44" s="15">
         <v>340000</v>
       </c>
       <c r="F44" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -2956,22 +2951,22 @@
         <v>46127</v>
       </c>
       <c r="B45" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C45" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D45" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E45" s="15">
         <v>1272000</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -2979,22 +2974,22 @@
         <v>46129</v>
       </c>
       <c r="B46" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C46" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E46" s="15">
         <v>546000</v>
       </c>
       <c r="F46" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -3002,22 +2997,22 @@
         <v>46131</v>
       </c>
       <c r="B47" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D47" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C47" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D47" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E47" s="15">
         <v>500000</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -3025,22 +3020,22 @@
         <v>46133</v>
       </c>
       <c r="B48" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D48" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E48" s="15">
         <v>327000</v>
       </c>
       <c r="F48" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -3048,22 +3043,22 @@
         <v>46167</v>
       </c>
       <c r="B49" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D49" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="C49" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D49" s="14" t="s">
-        <v>52</v>
       </c>
       <c r="E49" s="15">
         <v>18000000</v>
       </c>
       <c r="F49" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -3071,22 +3066,22 @@
         <v>46145</v>
       </c>
       <c r="B50" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D50" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C50" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D50" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E50" s="15">
         <v>5820000</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -3094,22 +3089,22 @@
         <v>46147</v>
       </c>
       <c r="B51" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C51" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D51" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E51" s="15">
         <v>2650000</v>
       </c>
       <c r="F51" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -3117,22 +3112,22 @@
         <v>46149</v>
       </c>
       <c r="B52" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C52" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D52" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E52" s="15">
         <v>4095000</v>
       </c>
       <c r="F52" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -3140,22 +3135,22 @@
         <v>46151</v>
       </c>
       <c r="B53" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D53" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C53" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E53" s="15">
         <v>900000</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -3163,22 +3158,22 @@
         <v>46153</v>
       </c>
       <c r="B54" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C54" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D54" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C54" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E54" s="15">
         <v>545000</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G54" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -3186,22 +3181,22 @@
         <v>46155</v>
       </c>
       <c r="B55" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C55" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C55" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D55" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E55" s="15">
         <v>329000</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G55" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -3209,22 +3204,22 @@
         <v>46157</v>
       </c>
       <c r="B56" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C56" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D56" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C56" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D56" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E56" s="15">
         <v>1236000</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G56" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3232,22 +3227,22 @@
         <v>46159</v>
       </c>
       <c r="B57" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D57" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C57" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D57" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E57" s="15">
         <v>528000</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G57" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3255,22 +3250,22 @@
         <v>46161</v>
       </c>
       <c r="B58" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D58" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C58" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D58" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E58" s="15">
         <v>485000</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G58" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3278,22 +3273,22 @@
         <v>46163</v>
       </c>
       <c r="B59" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C59" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D59" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C59" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D59" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E59" s="15">
         <v>318000</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G59" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -3301,22 +3296,22 @@
         <v>46198</v>
       </c>
       <c r="B60" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D60" s="14" t="s">
         <v>51</v>
-      </c>
-      <c r="C60" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D60" s="14" t="s">
-        <v>52</v>
       </c>
       <c r="E60" s="15">
         <v>18000000</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G60" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -3324,22 +3319,22 @@
         <v>46176</v>
       </c>
       <c r="B61" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C61" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D61" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E61" s="15">
         <v>5640000</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G61" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -3347,22 +3342,22 @@
         <v>46178</v>
       </c>
       <c r="B62" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C62" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C62" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D62" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E62" s="15">
         <v>2575000</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3370,22 +3365,22 @@
         <v>46180</v>
       </c>
       <c r="B63" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C63" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D63" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C63" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="D63" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E63" s="15">
         <v>3960000</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G63" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3393,22 +3388,22 @@
         <v>46182</v>
       </c>
       <c r="B64" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D64" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C64" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="D64" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E64" s="15">
         <v>873000</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -3416,22 +3411,22 @@
         <v>46184</v>
       </c>
       <c r="B65" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C65" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D65" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C65" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D65" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E65" s="15">
         <v>530000</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G65" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -3439,22 +3434,22 @@
         <v>46186</v>
       </c>
       <c r="B66" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C66" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C66" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D66" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E66" s="15">
         <v>318000</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -3462,22 +3457,22 @@
         <v>46188</v>
       </c>
       <c r="B67" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C67" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D67" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C67" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D67" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E67" s="15">
         <v>1200000</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G67" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -3485,22 +3480,22 @@
         <v>46190</v>
       </c>
       <c r="B68" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C68" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D68" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C68" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="D68" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E68" s="15">
         <v>654000</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G68" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -3508,22 +3503,22 @@
         <v>46192</v>
       </c>
       <c r="B69" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C69" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D69" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C69" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D69" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E69" s="15">
         <v>470000</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G69" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3531,22 +3526,22 @@
         <v>46194</v>
       </c>
       <c r="B70" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C70" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D70" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="C70" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D70" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="E70" s="15">
         <v>309000</v>
       </c>
       <c r="F70" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G70" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -12006,7 +12001,7 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -12025,7 +12020,7 @@
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -12044,7 +12039,7 @@
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B4" s="16">
         <v>1</v>
@@ -12083,10 +12078,10 @@
         <v>12</v>
       </c>
       <c r="N4" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="O4" s="11" t="s">
         <v>59</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -12671,7 +12666,7 @@
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B15" s="19">
         <f>SUM(B5:B14)</f>
@@ -12728,7 +12723,7 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B16" s="19">
         <f>SUMIFS('입력'!$E$5:$E$1004,'입력'!$B$5:$B$1004,"수입",'입력'!$A$5:$A$1004,"&gt;="&amp;DATE(Year,B$4,1),'입력'!$A$5:$A$1004,"&lt;"&amp;DATE(Year,B$4+1,1))</f>
@@ -12785,7 +12780,7 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B17" s="20">
         <f>B16-B15</f>
@@ -12842,7 +12837,7 @@
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" s="21">
         <f>IF(B16=0,"",B17/B16)</f>
@@ -13099,7 +13094,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -13108,7 +13103,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" s="22">
         <v>6</v>
@@ -13116,19 +13111,19 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="D5" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>69</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -13353,7 +13348,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B16" s="20">
         <f>SUM(B6:B15)</f>
@@ -13374,7 +13369,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -13462,7 +13457,7 @@
   <sheetData>
     <row r="1" spans="2:7">
       <c r="B1" s="26" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C1" s="26"/>
       <c r="D1" s="26"/>
@@ -13471,9 +13466,7 @@
       <c r="G1" s="26"/>
     </row>
     <row r="2" spans="2:7">
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -13482,22 +13475,22 @@
     </row>
     <row r="4" spans="2:7">
       <c r="B4" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="D4" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="E4" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="E4" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="27" t="s">
+      <c r="G4" s="27" t="s">
         <v>76</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="5" spans="2:7" ht="34" customHeight="1">
@@ -13558,7 +13551,7 @@
   <sheetData>
     <row r="1" spans="2:9">
       <c r="B1" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
@@ -13568,7 +13561,7 @@
     </row>
     <row r="3" spans="2:9">
       <c r="B3" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="32">
         <v>2026</v>
@@ -13576,7 +13569,7 @@
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="33">
         <v>0</v>
@@ -13584,33 +13577,33 @@
     </row>
     <row r="6" spans="2:9">
       <c r="B6" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="E6" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="G6" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="I6" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" spans="2:9">
       <c r="B7" s="34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" s="33">
         <v>6000000</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I7" s="14">
         <f>B7</f>
@@ -13619,16 +13612,16 @@
     </row>
     <row r="8" spans="2:9">
       <c r="B8" s="34" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" s="33">
         <v>2500000</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I8" s="14">
         <f>B8</f>
@@ -13637,16 +13630,16 @@
     </row>
     <row r="9" spans="2:9">
       <c r="B9" s="34" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" s="33">
         <v>4500000</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I9" s="14">
         <f>B9</f>
@@ -13655,13 +13648,13 @@
     </row>
     <row r="10" spans="2:9">
       <c r="B10" s="34" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" s="33">
         <v>900000</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I10" s="14">
         <f>B10</f>
@@ -13670,13 +13663,13 @@
     </row>
     <row r="11" spans="2:9">
       <c r="B11" s="34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="33">
         <v>500000</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I11" s="14">
         <f>B11</f>
@@ -13685,13 +13678,13 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="33">
         <v>350000</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I12" s="14">
         <f>B12</f>
@@ -13700,7 +13693,7 @@
     </row>
     <row r="13" spans="2:9">
       <c r="B13" s="34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="33">
         <v>1200000</v>
@@ -13712,7 +13705,7 @@
     </row>
     <row r="14" spans="2:9">
       <c r="B14" s="34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" s="33">
         <v>600000</v>
@@ -13724,7 +13717,7 @@
     </row>
     <row r="15" spans="2:9">
       <c r="B15" s="34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C15" s="33">
         <v>500000</v>
@@ -13736,7 +13729,7 @@
     </row>
     <row r="16" spans="2:9">
       <c r="B16" s="34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C16" s="33">
         <v>300000</v>
@@ -13754,7 +13747,7 @@
     </row>
     <row r="18" spans="2:9">
       <c r="B18" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="19">
         <f>SUM(C7:C16)</f>

--- a/public/fun/pack/xlsx/ledger/가계부_30_기업·소상공인_단풍든우체통.xlsx
+++ b/public/fun/pack/xlsx/ledger/가계부_30_기업·소상공인_단풍든우체통.xlsx
@@ -71,7 +71,7 @@
     <t>분류 이름을 바꾸면 요약·차트의 이름도 같이 바뀌어요. 가구 유형: 기업·소상공인</t>
   </si>
   <si>
-    <t>우체국보험 상담 안내 · 자유롭게 고쳐 쓰세요</t>
+    <t>반딧불이의 곳간 · 자유롭게 고쳐 쓰세요</t>
   </si>
   <si>
     <t>설정 — 내 상황에 맞게 고쳐요</t>
@@ -264,13 +264,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="m&quot;월&quot; d&quot;일&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0&quot;월&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0;[Red]-#,##0"/>
     <numFmt numFmtId="168" formatCode="0%"/>
     <numFmt numFmtId="169" formatCode="@"/>
+    <numFmt numFmtId="170" formatCode="&quot;올해&quot;"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -547,7 +548,7 @@
     <xf numFmtId="169" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
